--- a/Withdrawal_Statement.xlsx
+++ b/Withdrawal_Statement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dantez\Downloads\ofds\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFD9F5B-060D-4B35-89D1-DD8BD4057E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3088991-4659-4207-80C8-0FAF69D251A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Withdrawals" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>internal_client_code</t>
   </si>
@@ -151,54 +151,25 @@
     <t>note</t>
   </si>
   <si>
-    <t>AXIOM-001</t>
-  </si>
-  <si>
-    <t>John Smith</t>
-  </si>
-  <si>
     <t>Axiom</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>AXIOM-002</t>
-  </si>
-  <si>
-    <t>Jane Doe</t>
-  </si>
-  <si>
-    <t>AXIOM-003</t>
-  </si>
-  <si>
-    <t>Michael Johnson</t>
-  </si>
-  <si>
-    <t>ATIUM-007</t>
-  </si>
-  <si>
-    <t>Jennifer White</t>
-  </si>
-  <si>
-    <t>Atium</t>
-  </si>
-  <si>
-    <t>ATIUM-008</t>
-  </si>
-  <si>
-    <t>Andrew Harris</t>
+    <t>Joy Kendi Muthuri</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,8 +189,21 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,6 +220,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0066CC"/>
         <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -263,10 +253,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -286,8 +277,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -623,108 +617,60 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="8">
+        <v>126184</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="4">
         <v>3000</v>
       </c>
       <c r="E2" s="5">
-        <v>46261</v>
+        <v>46146</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E3" s="5">
-        <v>46261</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4">
-        <v>7000</v>
-      </c>
-      <c r="E4" s="5">
-        <v>46261</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2000</v>
-      </c>
-      <c r="E5" s="5">
-        <v>46261</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1000</v>
-      </c>
-      <c r="E6" s="5">
-        <v>46261</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
